--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_TRCOFF-CSTD-1-00-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_TRCOFF-CSTD-1-00-A-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\s10035azcfs0534.file.core.windows.net\metersoft\開発用\Toyota\BEV\設計成果物_MET\MCU-DT\02設計\01.シス検\C_TRCOFF-CSTD-0\02.ソフト設計書\01.変更点設計書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\BEV\BEV設計・実装\11月案件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5C49D8-5E4C-43CB-9DAF-AD49A6EA375C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4396D506-4130-4797-85EA-C12412AE3112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67200" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25974" yWindow="-109" windowWidth="26301" windowHeight="14305" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -551,7 +551,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2539" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2539" uniqueCount="289">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2523,14 +2523,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>VSC1S95</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VSC1S95</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>RWT_EN</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2549,9 +2541,6 @@
   <si>
     <t>BAT_AO</t>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VSC1S95_STS</t>
   </si>
   <si>
     <t>TRCOFF</t>
@@ -3041,6 +3030,10 @@
   </si>
   <si>
     <t>https://svn.geniie.net/bevs3/bevs3cdc/仕様書/MET/%231/tags/00.Product/v0.1.0/制御仕様/MET-C_TRCOFF-CSTD-1-00-A-C0/</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DDM1S17_STS</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -5076,16 +5069,37 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5130,31 +5144,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5207,49 +5200,7 @@
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -5293,38 +5244,8 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -6168,8 +6089,8 @@
       <xdr:rowOff>112058</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>683558</xdr:colOff>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>4101</xdr:colOff>
       <xdr:row>112</xdr:row>
       <xdr:rowOff>156881</xdr:rowOff>
     </xdr:to>
@@ -6186,8 +6107,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="15004676" y="12920382"/>
-          <a:ext cx="16741588" cy="8617323"/>
+          <a:off x="13621913" y="12564542"/>
+          <a:ext cx="15133522" cy="8326181"/>
           <a:chOff x="15329647" y="17850971"/>
           <a:chExt cx="17930232" cy="10185684"/>
         </a:xfrm>
@@ -6938,8 +6859,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="15888100" y="1725705"/>
-          <a:ext cx="19294846" cy="19531852"/>
+          <a:off x="14440849" y="1705196"/>
+          <a:ext cx="17424733" cy="18911088"/>
           <a:chOff x="16966933" y="1566571"/>
           <a:chExt cx="19558166" cy="19531575"/>
         </a:xfrm>
@@ -8138,132 +8059,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>44824</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>56028</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>123265</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>156883</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="正方形/長方形 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13872883" y="56028"/>
-          <a:ext cx="1591235" cy="649943"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>面企画</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>#2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>からの</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>変更点は赤字で記載</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>19</xdr:col>
@@ -8629,6 +8424,282 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>2060191</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>2</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>568329</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>30446</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="線吹き出し 1 (枠付き) 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A56A3058-91A1-4D0A-8FBF-115355A5CB15}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11589843" y="5145404"/>
+          <a:ext cx="2253017" cy="1167102"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 52087"/>
+            <a:gd name="adj2" fmla="val 100142"/>
+            <a:gd name="adj3" fmla="val 80976"/>
+            <a:gd name="adj4" fmla="val 318445"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>仕様の表記が誤っているが</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>BA</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>表より以下となる。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>〇「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>DDM1S17</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>✖「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>VSC1S95</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>548031</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>131934</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>426246</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7C32557-42AC-4974-B1C2-5B6B64BE14BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18775139" y="5926855"/>
+          <a:ext cx="1116359" cy="842344"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8921,7 +8992,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
@@ -8997,7 +9068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
+    <row r="6" spans="2:24" ht="13.6" thickBot="1"/>
     <row r="7" spans="2:24">
       <c r="C7" s="232" t="s">
         <v>0</v>
@@ -9024,7 +9095,7 @@
       <c r="Q7" s="236"/>
       <c r="R7" s="236"/>
       <c r="S7" s="229" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="T7" s="230"/>
       <c r="U7" s="230"/>
@@ -9032,7 +9103,7 @@
       <c r="W7" s="230"/>
       <c r="X7" s="231"/>
     </row>
-    <row r="8" spans="2:24" ht="27.75" thickBot="1">
+    <row r="8" spans="2:24" ht="26.5" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>89</v>
       </c>
@@ -9085,7 +9156,7 @@
         <v>11</v>
       </c>
       <c r="S8" s="223" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="T8" s="16" t="s">
         <v>7</v>
@@ -9103,7 +9174,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="14.25" thickTop="1">
+    <row r="9" spans="2:24" ht="13.6" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -9139,19 +9210,19 @@
         <v>31</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N9" s="215">
         <v>43943</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="P9" s="215">
         <v>43943</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="R9" s="215">
         <v>43923</v>
@@ -9175,16 +9246,16 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="108">
+    <row r="10" spans="2:24" ht="103.25">
       <c r="B10" s="9">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D10" s="217" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>31</v>
@@ -9211,19 +9282,19 @@
         <v>31</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N10" s="218">
         <v>44064</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="P10" s="218">
         <v>44064</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="R10" s="218">
         <v>44064</v>
@@ -9247,16 +9318,16 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="2:24" ht="121.5">
+    <row r="11" spans="2:24" ht="116.15">
       <c r="B11" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D11" s="217" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>31</v>
@@ -9287,7 +9358,7 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="R11" s="218">
         <v>44575</v>
@@ -9311,22 +9382,22 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="2:24" ht="216">
+    <row r="12" spans="2:24" ht="206.5">
       <c r="B12" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D12" s="217" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>31</v>
@@ -9369,13 +9440,13 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="X12" s="216">
         <v>45348</v>
       </c>
     </row>
-    <row r="13" spans="2:24" ht="14.25" thickBot="1">
+    <row r="13" spans="2:24" ht="13.6" thickBot="1">
       <c r="B13" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9426,7 +9497,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="4.625" customWidth="1"/>
     <col min="3" max="3" width="3.5" customWidth="1"/>
@@ -9444,13 +9515,13 @@
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14.25" thickBot="1">
+    <row r="6" spans="2:5" ht="13.6" thickBot="1">
       <c r="B6" s="139" t="s">
         <v>126</v>
       </c>
       <c r="C6" s="139"/>
     </row>
-    <row r="7" spans="2:5" ht="14.25" thickBot="1">
+    <row r="7" spans="2:5" ht="13.6" thickBot="1">
       <c r="C7" s="66" t="s">
         <v>128</v>
       </c>
@@ -9467,7 +9538,7 @@
         <v>137</v>
       </c>
       <c r="E8" s="142" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -9475,7 +9546,7 @@
       <c r="D9" s="151"/>
       <c r="E9" s="150"/>
     </row>
-    <row r="10" spans="2:5" ht="14.25" thickBot="1">
+    <row r="10" spans="2:5" ht="13.6" thickBot="1">
       <c r="C10" s="147"/>
       <c r="D10" s="77"/>
       <c r="E10" s="5"/>
@@ -9483,14 +9554,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="145"/>
     </row>
-    <row r="12" spans="2:5" ht="14.25" thickBot="1">
+    <row r="12" spans="2:5" ht="13.6" thickBot="1">
       <c r="B12" s="140" t="s">
         <v>127</v>
       </c>
       <c r="C12" s="73"/>
       <c r="D12" s="73"/>
     </row>
-    <row r="13" spans="2:5" ht="14.25" thickBot="1">
+    <row r="13" spans="2:5" ht="13.6" thickBot="1">
       <c r="B13" s="141"/>
       <c r="C13" s="146" t="s">
         <v>128</v>
@@ -9502,7 +9573,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="14.25" thickTop="1">
+    <row r="14" spans="2:5" ht="13.6" thickTop="1">
       <c r="C14" s="143">
         <v>0</v>
       </c>
@@ -9579,17 +9650,17 @@
         <v>161</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="14.25" thickBot="1">
+    <row r="21" spans="2:5" ht="13.6" thickBot="1">
       <c r="C21" s="147"/>
       <c r="D21" s="77"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="14.25" thickBot="1">
+    <row r="24" spans="2:5" ht="13.6" thickBot="1">
       <c r="B24" s="139" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="14.25" thickBot="1">
+    <row r="25" spans="2:5" ht="13.6" thickBot="1">
       <c r="C25" s="146" t="s">
         <v>128</v>
       </c>
@@ -9611,7 +9682,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="120" customHeight="1">
+    <row r="27" spans="2:5" ht="120.1" customHeight="1">
       <c r="C27" s="144">
         <v>1</v>
       </c>
@@ -9676,12 +9747,12 @@
       <c r="D33" s="76"/>
       <c r="E33" s="65"/>
     </row>
-    <row r="34" spans="2:5" ht="14.25" thickBot="1">
+    <row r="34" spans="2:5" ht="13.6" thickBot="1">
       <c r="C34" s="147"/>
       <c r="D34" s="77"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="14.25" thickBot="1">
+    <row r="37" spans="2:5" ht="13.6" thickBot="1">
       <c r="B37" s="139" t="s">
         <v>157</v>
       </c>
@@ -9693,7 +9764,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="14.25" thickBot="1">
+    <row r="39" spans="2:5" ht="13.6" thickBot="1">
       <c r="C39" s="239"/>
       <c r="D39" s="240"/>
       <c r="E39" s="5" t="s">
@@ -9720,7 +9791,7 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
@@ -9730,121 +9801,121 @@
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.6" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="241" t="s">
+      <c r="B2" s="266" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="242"/>
-      <c r="D2" s="247" t="s">
-        <v>289</v>
-      </c>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="249"/>
+      <c r="C2" s="267"/>
+      <c r="D2" s="254" t="s">
+        <v>286</v>
+      </c>
+      <c r="E2" s="255"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="256"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="243" t="s">
+      <c r="B3" s="241" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="244"/>
-      <c r="D3" s="250" t="s">
-        <v>290</v>
-      </c>
-      <c r="E3" s="251"/>
-      <c r="F3" s="251"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252"/>
-    </row>
-    <row r="4" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B4" s="245" t="s">
+      <c r="C3" s="242"/>
+      <c r="D3" s="257" t="s">
+        <v>287</v>
+      </c>
+      <c r="E3" s="258"/>
+      <c r="F3" s="258"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259"/>
+    </row>
+    <row r="4" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B4" s="252" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="246"/>
-      <c r="D4" s="253" t="str">
+      <c r="C4" s="253"/>
+      <c r="D4" s="260" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_C_TRCOFF-CSTD-1-00-A-C0.c</v>
       </c>
-      <c r="E4" s="254"/>
-      <c r="F4" s="254"/>
-      <c r="G4" s="254"/>
-      <c r="H4" s="255"/>
-    </row>
-    <row r="5" spans="2:14" ht="14.25" thickBot="1">
+      <c r="E4" s="261"/>
+      <c r="F4" s="261"/>
+      <c r="G4" s="261"/>
+      <c r="H4" s="262"/>
+    </row>
+    <row r="5" spans="2:14" ht="13.6" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="241" t="s">
+      <c r="B6" s="266" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="242"/>
-      <c r="D6" s="256" t="str">
+      <c r="C6" s="267"/>
+      <c r="D6" s="263" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>C_TRCOFF</v>
       </c>
-      <c r="E6" s="257"/>
-      <c r="F6" s="257"/>
-      <c r="G6" s="257"/>
-      <c r="H6" s="258"/>
+      <c r="E6" s="264"/>
+      <c r="F6" s="264"/>
+      <c r="G6" s="264"/>
+      <c r="H6" s="265"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="243" t="s">
+      <c r="B7" s="241" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="244"/>
-      <c r="D7" s="259">
+      <c r="C7" s="242"/>
+      <c r="D7" s="243">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="260"/>
-      <c r="F7" s="260"/>
-      <c r="G7" s="260"/>
-      <c r="H7" s="261"/>
+      <c r="E7" s="244"/>
+      <c r="F7" s="244"/>
+      <c r="G7" s="244"/>
+      <c r="H7" s="245"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="243" t="s">
+      <c r="B8" s="241" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="244"/>
-      <c r="D8" s="259" t="str">
+      <c r="C8" s="242"/>
+      <c r="D8" s="243" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_C_TRCOFF_MTRX</v>
       </c>
-      <c r="E8" s="260"/>
-      <c r="F8" s="260"/>
-      <c r="G8" s="260"/>
-      <c r="H8" s="261"/>
+      <c r="E8" s="244"/>
+      <c r="F8" s="244"/>
+      <c r="G8" s="244"/>
+      <c r="H8" s="245"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="243" t="s">
+      <c r="B9" s="241" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="244"/>
-      <c r="D9" s="262" t="s">
+      <c r="C9" s="242"/>
+      <c r="D9" s="246" t="s">
         <v>194</v>
       </c>
-      <c r="E9" s="263"/>
-      <c r="F9" s="263"/>
-      <c r="G9" s="263"/>
-      <c r="H9" s="264"/>
-    </row>
-    <row r="10" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B10" s="245" t="s">
+      <c r="E9" s="247"/>
+      <c r="F9" s="247"/>
+      <c r="G9" s="247"/>
+      <c r="H9" s="248"/>
+    </row>
+    <row r="10" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B10" s="252" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="246"/>
-      <c r="D10" s="265"/>
-      <c r="E10" s="266"/>
-      <c r="F10" s="266"/>
-      <c r="G10" s="266"/>
-      <c r="H10" s="267"/>
-    </row>
-    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
-    <row r="12" spans="2:14" ht="14.25" thickBot="1">
+      <c r="C10" s="253"/>
+      <c r="D10" s="249"/>
+      <c r="E10" s="250"/>
+      <c r="F10" s="250"/>
+      <c r="G10" s="250"/>
+      <c r="H10" s="251"/>
+    </row>
+    <row r="11" spans="2:14" ht="13.6" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.6" thickBot="1">
       <c r="B12" s="130" t="s">
         <v>34</v>
       </c>
@@ -9879,12 +9950,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="14.25" thickTop="1">
+    <row r="13" spans="2:14" ht="13.6" thickTop="1">
       <c r="B13" s="95">
         <v>1</v>
       </c>
       <c r="C13" s="184" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D13" s="185" t="s">
         <v>48</v>
@@ -10732,7 +10803,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="14.25" thickBot="1">
+    <row r="37" spans="2:14" ht="13.6" thickBot="1">
       <c r="B37" s="86">
         <v>25</v>
       </c>
@@ -10773,47 +10844,37 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="C15:C37">
-    <cfRule type="expression" dxfId="15" priority="10">
-      <formula>14&lt;LEN($D$6)+LEN($C15)</formula>
+  <conditionalFormatting sqref="C13:C37">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>14&lt;LEN($D$6)+LEN($C13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="NG">
+      <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="14" priority="9">
+    <cfRule type="expression" dxfId="4" priority="9">
       <formula>14 &lt; LEN($D$6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5">
-    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="NG">
-      <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="12" priority="5">
-      <formula>14&lt;LEN($D$6)+LEN($C14)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="11" priority="1">
-      <formula>14&lt;LEN($D$6)+LEN($C13)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -10838,7 +10899,7 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
@@ -10852,7 +10913,7 @@
     <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="14.25" thickBot="1">
+    <row r="2" spans="2:18" ht="13.6" thickBot="1">
       <c r="B2" t="s">
         <v>182</v>
       </c>
@@ -10860,7 +10921,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="14.25" thickBot="1">
+    <row r="3" spans="2:18" ht="13.6" thickBot="1">
       <c r="B3" s="130" t="s">
         <v>34</v>
       </c>
@@ -10898,7 +10959,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B4" s="160">
         <v>0</v>
       </c>
@@ -10926,7 +10987,7 @@
       </c>
       <c r="R4" s="127"/>
     </row>
-    <row r="5" spans="2:18" ht="14.25" thickTop="1">
+    <row r="5" spans="2:18" ht="13.6" thickTop="1">
       <c r="B5" s="163">
         <v>1</v>
       </c>
@@ -11454,7 +11515,7 @@
       <c r="Q28" s="134"/>
       <c r="R28" s="103"/>
     </row>
-    <row r="29" spans="2:18" ht="14.25" thickBot="1">
+    <row r="29" spans="2:18" ht="13.6" thickBot="1">
       <c r="B29" s="164">
         <v>25</v>
       </c>
@@ -11476,7 +11537,7 @@
       <c r="Q29" s="132"/>
       <c r="R29" s="105"/>
     </row>
-    <row r="32" spans="2:18" ht="14.25" thickBot="1">
+    <row r="32" spans="2:18" ht="13.6" thickBot="1">
       <c r="B32" t="s">
         <v>183</v>
       </c>
@@ -11484,7 +11545,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="14.25" thickBot="1">
+    <row r="33" spans="2:18" ht="13.6" thickBot="1">
       <c r="B33" s="130" t="s">
         <v>34</v>
       </c>
@@ -11516,7 +11577,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B34" s="160">
         <v>0</v>
       </c>
@@ -11542,7 +11603,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="14.25" thickTop="1">
+    <row r="35" spans="2:18" ht="13.6" thickTop="1">
       <c r="B35" s="163">
         <v>1</v>
       </c>
@@ -12070,7 +12131,7 @@
       <c r="Q58" s="134"/>
       <c r="R58" s="165"/>
     </row>
-    <row r="59" spans="2:18" ht="14.25" thickBot="1">
+    <row r="59" spans="2:18" ht="13.6" thickBot="1">
       <c r="B59" s="164">
         <v>25</v>
       </c>
@@ -12118,7 +12179,7 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="28.375" customWidth="1"/>
     <col min="3" max="3" width="15.875" customWidth="1"/>
@@ -12133,12 +12194,12 @@
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.25" thickBot="1">
+    <row r="1" spans="2:21" ht="13.6" thickBot="1">
       <c r="C1" s="79" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="14.25" thickBot="1">
+    <row r="2" spans="2:21" ht="13.6" thickBot="1">
       <c r="B2" s="87" t="s">
         <v>58</v>
       </c>
@@ -12182,7 +12243,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14.3" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="23"/>
       <c r="C3" s="41" t="s">
         <v>105</v>
@@ -12203,12 +12264,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="14.25" thickTop="1">
+    <row r="4" spans="2:21" ht="13.6" thickTop="1">
       <c r="B4" s="98" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C4" s="96" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D4" s="106">
         <v>0</v>
@@ -12217,7 +12278,7 @@
         <v>123</v>
       </c>
       <c r="F4" s="176" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G4" s="175" t="s">
         <v>123</v>
@@ -12471,7 +12532,7 @@
       </c>
       <c r="U12" s="26"/>
     </row>
-    <row r="13" spans="2:21" ht="14.25" thickBot="1">
+    <row r="13" spans="2:21" ht="13.6" thickBot="1">
       <c r="B13" s="98"/>
       <c r="C13" s="97"/>
       <c r="D13" s="107"/>
@@ -14722,7 +14783,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="14.25" thickBot="1">
+    <row r="103" spans="2:15" ht="13.6" thickBot="1">
       <c r="B103" s="43"/>
       <c r="C103" s="44"/>
       <c r="D103" s="104"/>
@@ -14753,13 +14814,8 @@
     <protectedRange sqref="B4:L103" name="範囲1"/>
   </protectedRanges>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="M4:M103">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
-      <formula>32</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="M3:M103">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>32</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14797,7 +14853,7 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
@@ -14927,7 +14983,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="213" customHeight="1" thickBot="1">
+    <row r="3" spans="1:49" ht="212.95" customHeight="1" thickBot="1">
       <c r="B3" s="119" t="s">
         <v>195</v>
       </c>
@@ -15023,17 +15079,17 @@
         <v>66</v>
       </c>
       <c r="AH3" s="214" t="s">
-        <v>225</v>
+        <v>288</v>
       </c>
       <c r="AI3" s="208" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AJ3" s="271"/>
       <c r="AR3" s="80" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="14.25" thickBot="1">
+    <row r="4" spans="1:49" ht="13.6" thickBot="1">
       <c r="A4" s="272" t="s">
         <v>63</v>
       </c>
@@ -15081,7 +15137,7 @@
       <c r="AV4" s="69"/>
       <c r="AW4" s="70"/>
     </row>
-    <row r="5" spans="1:49" ht="14.25" thickBot="1">
+    <row r="5" spans="1:49" ht="13.6" thickBot="1">
       <c r="A5" s="274"/>
       <c r="B5" s="275"/>
       <c r="C5" s="125"/>
@@ -15237,7 +15293,7 @@
         <v>198</v>
       </c>
       <c r="AG6" s="178" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AH6" s="178">
         <v>0</v>
@@ -15265,7 +15321,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_UNKNOWN,                                                     /* 00 UNKNOWN                                         */</v>
       </c>
       <c r="AU6" s="53" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AV6" s="38" t="s">
         <v>68</v>
@@ -15369,7 +15425,7 @@
         <v>198</v>
       </c>
       <c r="AG7" s="178" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AH7" s="178">
         <v>0</v>
@@ -15378,7 +15434,7 @@
         <v>1</v>
       </c>
       <c r="AJ7" s="41" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AL7" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -15502,7 +15558,7 @@
         <v>199</v>
       </c>
       <c r="AG8" s="178" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AH8" s="178">
         <v>1</v>
@@ -15635,7 +15691,7 @@
         <v>199</v>
       </c>
       <c r="AG9" s="51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AH9" s="51">
         <v>1</v>
@@ -15765,13 +15821,13 @@
         <v>200</v>
       </c>
       <c r="AG10" s="51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AH10" s="51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AI10" s="51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AJ10" s="41"/>
       <c r="AL10" t="str">
@@ -15896,13 +15952,13 @@
         <v>198</v>
       </c>
       <c r="AG11" s="51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AH11" s="51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AI11" s="51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AJ11" s="41"/>
       <c r="AL11" t="str">
@@ -16027,13 +16083,13 @@
         <v>200</v>
       </c>
       <c r="AG12" s="51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AH12" s="51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AI12" s="51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AJ12" s="41"/>
       <c r="AL12" t="str">
@@ -16155,13 +16211,13 @@
         <v>198</v>
       </c>
       <c r="AG13" s="51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AH13" s="51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AI13" s="51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AJ13" s="41"/>
       <c r="AL13" t="str">
@@ -16574,7 +16630,7 @@
         <v/>
       </c>
       <c r="AU16" s="53" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AV16" s="39" t="s">
         <v>76</v>
@@ -16584,7 +16640,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="14.25" thickBot="1">
+    <row r="17" spans="2:49" ht="13.6" thickBot="1">
       <c r="B17" s="121"/>
       <c r="C17" s="37">
         <f t="shared" si="2"/>
@@ -16704,7 +16760,7 @@
         <v/>
       </c>
       <c r="AU17" s="54" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AV17" s="40" t="s">
         <v>77</v>
@@ -22954,7 +23010,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="14.25" thickBot="1">
+    <row r="70" spans="1:46" ht="13.6" thickBot="1">
       <c r="A70" s="46" t="s">
         <v>64</v>
       </c>
@@ -43549,41 +43605,17 @@
     <mergeCell ref="A4:B5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="D34:AI69 D10:AE33">
-    <cfRule type="cellIs" dxfId="8" priority="34" operator="equal">
+  <conditionalFormatting sqref="D6:AI69">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"×"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR5:AS70">
-    <cfRule type="expression" dxfId="6" priority="33">
+    <cfRule type="expression" dxfId="0" priority="33">
       <formula>$B$3="Index Table"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D6:AE9">
-    <cfRule type="cellIs" dxfId="5" priority="21" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="22" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF14:AI33 AF6:AF13">
-    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="10" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG6:AI13">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"×"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -43613,7 +43645,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:Q14"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="35.375" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="3.375" customWidth="1"/>
@@ -43626,12 +43658,12 @@
     <col min="18" max="18" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="15" thickBot="1">
+    <row r="2" spans="2:17" ht="15.65" thickBot="1">
       <c r="B2" s="219" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="3" spans="2:17" ht="15" thickBot="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" ht="15.65" thickBot="1">
       <c r="B3" s="84" t="s">
         <v>206</v>
       </c>
@@ -43753,7 +43785,7 @@
       <c r="P6" s="190"/>
       <c r="Q6" s="127"/>
     </row>
-    <row r="7" spans="2:17" ht="27">
+    <row r="7" spans="2:17" ht="25.85">
       <c r="B7" s="62" t="s">
         <v>27</v>
       </c>
@@ -43768,10 +43800,10 @@
       <c r="I7" s="280"/>
       <c r="J7" s="282"/>
       <c r="K7" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="L7" s="197" t="s">
-        <v>219</v>
+        <v>288</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="M7" s="27"/>
       <c r="N7" s="196"/>
@@ -43779,39 +43811,39 @@
       <c r="P7" s="190"/>
       <c r="Q7" s="127"/>
     </row>
-    <row r="8" spans="2:17" ht="166.5" customHeight="1">
+    <row r="8" spans="2:17" ht="166.6" customHeight="1">
       <c r="B8" s="61" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="211" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D8" s="211" t="s">
         <v>62</v>
       </c>
       <c r="E8" s="211" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F8" s="211" t="s">
         <v>204</v>
       </c>
       <c r="G8" s="211" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H8" s="211" t="s">
         <v>205</v>
       </c>
       <c r="I8" s="211" t="s">
+        <v>221</v>
+      </c>
+      <c r="J8" s="211" t="s">
+        <v>222</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="L8" s="197" t="s">
         <v>223</v>
-      </c>
-      <c r="J8" s="211" t="s">
-        <v>224</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="L8" s="197" t="s">
-        <v>226</v>
       </c>
       <c r="M8" s="26" t="s">
         <v>29</v>
@@ -43821,45 +43853,45 @@
       <c r="P8" s="190"/>
       <c r="Q8" s="127"/>
     </row>
-    <row r="9" spans="2:17" ht="41.25" thickBot="1">
+    <row r="9" spans="2:17" ht="39.4" thickBot="1">
       <c r="B9" s="63" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="153" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D9" s="153" t="s">
         <v>214</v>
       </c>
       <c r="E9" s="153" t="s">
+        <v>224</v>
+      </c>
+      <c r="F9" s="153" t="s">
+        <v>225</v>
+      </c>
+      <c r="G9" s="153" t="s">
+        <v>226</v>
+      </c>
+      <c r="H9" s="153" t="s">
+        <v>226</v>
+      </c>
+      <c r="I9" s="153" t="s">
+        <v>226</v>
+      </c>
+      <c r="J9" s="153" t="s">
         <v>227</v>
       </c>
-      <c r="F9" s="153" t="s">
+      <c r="K9" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="G9" s="153" t="s">
+      <c r="L9" s="198" t="s">
         <v>229</v>
       </c>
-      <c r="H9" s="153" t="s">
-        <v>229</v>
-      </c>
-      <c r="I9" s="153" t="s">
-        <v>229</v>
-      </c>
-      <c r="J9" s="153" t="s">
+      <c r="M9" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="N9" s="212" t="s">
         <v>230</v>
-      </c>
-      <c r="K9" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="L9" s="198" t="s">
-        <v>232</v>
-      </c>
-      <c r="M9" s="28" t="s">
-        <v>256</v>
-      </c>
-      <c r="N9" s="212" t="s">
-        <v>233</v>
       </c>
       <c r="O9" s="221" t="s">
         <v>203</v>
@@ -43867,9 +43899,9 @@
       <c r="P9" s="199"/>
       <c r="Q9" s="128"/>
     </row>
-    <row r="10" spans="2:17" ht="14.25" thickTop="1">
+    <row r="10" spans="2:17" ht="13.6" thickTop="1">
       <c r="B10" s="64" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C10" s="154" t="s">
         <v>154</v>
@@ -43896,13 +43928,13 @@
         <v>154</v>
       </c>
       <c r="K10" s="30" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="L10" s="200" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="M10" s="31" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="N10" s="201" t="s">
         <v>213</v>
@@ -43915,7 +43947,7 @@
     </row>
     <row r="11" spans="2:17">
       <c r="B11" s="202" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C11" s="155" t="s">
         <v>154</v>
@@ -43942,16 +43974,16 @@
         <v>154</v>
       </c>
       <c r="K11" s="207" t="s">
+        <v>235</v>
+      </c>
+      <c r="L11" s="203" t="s">
+        <v>236</v>
+      </c>
+      <c r="M11" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="N11" s="204" t="s">
         <v>238</v>
-      </c>
-      <c r="L11" s="203" t="s">
-        <v>239</v>
-      </c>
-      <c r="M11" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="N11" s="204" t="s">
-        <v>241</v>
       </c>
       <c r="O11" s="220" t="s">
         <v>203</v>
@@ -43961,7 +43993,7 @@
     </row>
     <row r="12" spans="2:17">
       <c r="B12" s="202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C12" s="155" t="s">
         <v>154</v>
@@ -43988,16 +44020,16 @@
         <v>154</v>
       </c>
       <c r="K12" s="207" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L12" s="203" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="M12" s="32" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="N12" s="204" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O12" s="51" t="s">
         <v>213</v>
@@ -44007,7 +44039,7 @@
     </row>
     <row r="13" spans="2:17">
       <c r="B13" s="202" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C13" s="155" t="s">
         <v>154</v>
@@ -44034,26 +44066,26 @@
         <v>154</v>
       </c>
       <c r="K13" s="207" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L13" s="203" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="M13" s="32" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="N13" s="204" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O13" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P13" s="192"/>
       <c r="Q13" s="129"/>
     </row>
-    <row r="14" spans="2:17" ht="14.25" thickBot="1">
+    <row r="14" spans="2:17" ht="13.6" thickBot="1">
       <c r="B14" s="179" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C14" s="180" t="s">
         <v>154</v>
@@ -44080,19 +44112,19 @@
         <v>154</v>
       </c>
       <c r="K14" s="181" t="s">
+        <v>245</v>
+      </c>
+      <c r="L14" s="205" t="s">
+        <v>246</v>
+      </c>
+      <c r="M14" s="182" t="s">
+        <v>247</v>
+      </c>
+      <c r="N14" s="206" t="s">
+        <v>241</v>
+      </c>
+      <c r="O14" s="213" t="s">
         <v>248</v>
-      </c>
-      <c r="L14" s="205" t="s">
-        <v>249</v>
-      </c>
-      <c r="M14" s="182" t="s">
-        <v>250</v>
-      </c>
-      <c r="N14" s="206" t="s">
-        <v>244</v>
-      </c>
-      <c r="O14" s="213" t="s">
-        <v>251</v>
       </c>
       <c r="P14" s="193"/>
       <c r="Q14" s="183"/>
@@ -44118,14 +44150,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="14.25" thickBot="1">
+    <row r="2" spans="2:4" ht="13.6" thickBot="1">
       <c r="B2" s="72" t="s">
         <v>82</v>
       </c>
@@ -44135,7 +44167,7 @@
       </c>
       <c r="D2" s="73"/>
     </row>
-    <row r="3" spans="2:4" ht="14.25" thickBot="1">
+    <row r="3" spans="2:4" ht="13.6" thickBot="1">
       <c r="B3" s="66" t="s">
         <v>82</v>
       </c>
@@ -44146,7 +44178,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="14.25" thickTop="1">
+    <row r="4" spans="2:4" ht="13.6" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -44157,7 +44189,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="40.5">
+    <row r="5" spans="2:4" ht="38.75">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -44168,7 +44200,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="27">
+    <row r="6" spans="2:4" ht="25.85">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -44179,7 +44211,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="54">
+    <row r="7" spans="2:4" ht="51.65">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -44190,7 +44222,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="81">
+    <row r="8" spans="2:4" ht="77.45">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -44201,7 +44233,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="41.25" customHeight="1">
+    <row r="9" spans="2:4" ht="41.3" customHeight="1">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -44212,7 +44244,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="27">
+    <row r="10" spans="2:4" ht="25.85">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -44223,7 +44255,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="27">
+    <row r="11" spans="2:4" ht="25.85">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -44234,7 +44266,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="27">
+    <row r="12" spans="2:4" ht="25.85">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -44245,7 +44277,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="27">
+    <row r="13" spans="2:4" ht="25.85">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -44256,7 +44288,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="27">
+    <row r="14" spans="2:4" ht="25.85">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -44267,7 +44299,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="135">
+    <row r="15" spans="2:4" ht="129.1">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -44289,7 +44321,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="27">
+    <row r="17" spans="2:4" ht="25.85">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -44300,7 +44332,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="67.5">
+    <row r="18" spans="2:4" ht="90.35">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -44311,7 +44343,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="40.5">
+    <row r="19" spans="2:4" ht="38.75">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -44322,7 +44354,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="64.5" customHeight="1">
+    <row r="20" spans="2:4" ht="64.55" customHeight="1">
       <c r="B20" s="2">
         <v>16</v>
       </c>
@@ -44344,37 +44376,37 @@
         <v>186</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="27">
+    <row r="22" spans="2:4" ht="25.85">
       <c r="B22" s="2">
         <v>18</v>
       </c>
       <c r="C22" s="76" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D22" s="78" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="27">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="25.85">
       <c r="B23" s="2">
         <v>19</v>
       </c>
       <c r="C23" s="76" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D23" s="78" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" ht="94.5">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="90.35">
       <c r="B24" s="2">
         <v>20</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D24" s="78" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="25" spans="2:4">
@@ -44387,7 +44419,7 @@
       <c r="C26" s="76"/>
       <c r="D26" s="65"/>
     </row>
-    <row r="27" spans="2:4" ht="14.25" thickBot="1">
+    <row r="27" spans="2:4" ht="13.6" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="77"/>
       <c r="D27" s="5"/>
